--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/21,09,26 Останкино КИ и ЗПФ/машина САП 29,09 Бердянск_Мариуполь КИ/Заказ Новое Время_29,09,26_Мариуполь.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/21,09,26 Останкино КИ и ЗПФ/машина САП 29,09 Бердянск_Мариуполь КИ/Заказ Новое Время_29,09,26_Мариуполь.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\21,09,26 Останкино КИ и ЗПФ\машина САП 29,09 Бердянск_Мариуполь КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165578CD-015B-447F-B285-8A2D03601D74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A003FD23-3386-49FC-9EE2-E6820F03EE0D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$163</definedName>
     <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$570</definedName>
     <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$570</definedName>
   </definedNames>
@@ -5243,7 +5243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1658"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="K9" s="26"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="45"/>
       <c r="B10" s="40" t="s">
         <v>23</v>
@@ -5493,7 +5493,7 @@
       <c r="J12" s="27"/>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" spans="1:12" s="88" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="88" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="93" t="str">
         <f t="shared" si="0"/>
         <v>7539</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="K13" s="25"/>
     </row>
-    <row r="14" spans="1:12" s="88" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="88" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="93" t="str">
         <f t="shared" si="0"/>
         <v>7536</v>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="K14" s="25"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="93" t="str">
         <f t="shared" si="0"/>
         <v>6861</v>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="J15" s="27"/>
     </row>
-    <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="93" t="str">
         <f t="shared" si="0"/>
         <v>6862</v>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="J16" s="27"/>
     </row>
-    <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="93" t="str">
         <f t="shared" si="0"/>
         <v>6498</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="J20" s="27"/>
     </row>
-    <row r="21" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="93" t="str">
         <f t="shared" si="0"/>
         <v>7334</v>
@@ -5905,7 +5905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="93" t="str">
         <f t="shared" si="0"/>
         <v>4561</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="J27" s="27"/>
     </row>
-    <row r="28" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="93" t="str">
         <f t="shared" si="0"/>
         <v>8014</v>
@@ -6049,7 +6049,7 @@
       <c r="I30" s="27"/>
       <c r="J30" s="27"/>
     </row>
-    <row r="31" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="93" t="str">
         <f t="shared" si="0"/>
         <v>7343</v>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="J32" s="27"/>
     </row>
-    <row r="33" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="str">
         <f t="shared" si="0"/>
         <v>7231</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="J33" s="27"/>
     </row>
-    <row r="34" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="45"/>
       <c r="B34" s="40" t="s">
         <v>53</v>
@@ -6157,7 +6157,7 @@
       <c r="I34" s="40"/>
       <c r="J34" s="41"/>
     </row>
-    <row r="35" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="93" t="str">
         <f t="shared" ref="A35:A65" si="1">RIGHT(D35,4)</f>
         <v>6602</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J35" s="27"/>
     </row>
-    <row r="36" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7601</v>
@@ -6281,7 +6281,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6759</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="J39" s="27"/>
     </row>
-    <row r="40" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6761</v>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="J40" s="27"/>
     </row>
-    <row r="41" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6829</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="J42" s="27"/>
     </row>
-    <row r="43" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7075</v>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="J43" s="27"/>
     </row>
-    <row r="44" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7074</v>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="J49" s="27"/>
     </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7271</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="J51" s="27"/>
     </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6767</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="J52" s="27"/>
     </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6475</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="J55" s="27"/>
     </row>
-    <row r="56" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7276</v>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="J56" s="27"/>
     </row>
-    <row r="57" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6762</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="J57" s="27"/>
     </row>
-    <row r="58" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6764</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="J58" s="27"/>
     </row>
-    <row r="59" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7066</v>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="J59" s="27"/>
     </row>
-    <row r="60" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7070</v>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="J62" s="27"/>
     </row>
-    <row r="63" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6254</v>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="J63" s="27"/>
     </row>
-    <row r="64" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="93" t="str">
         <f t="shared" si="1"/>
         <v>6837</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="J64" s="27"/>
     </row>
-    <row r="65" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="93" t="str">
         <f t="shared" si="1"/>
         <v>7044</v>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="J65" s="27"/>
     </row>
-    <row r="66" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="45"/>
       <c r="B66" s="40" t="s">
         <v>87</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J70" s="27"/>
     </row>
-    <row r="71" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="93" t="str">
         <f t="shared" si="2"/>
         <v>6609</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="J71" s="27"/>
     </row>
-    <row r="72" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="93" t="str">
         <f t="shared" si="2"/>
         <v>7059</v>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="J72" s="27"/>
     </row>
-    <row r="73" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="45"/>
       <c r="B73" s="40" t="s">
         <v>94</v>
@@ -7333,7 +7333,7 @@
       <c r="I73" s="40"/>
       <c r="J73" s="41"/>
     </row>
-    <row r="74" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="93" t="str">
         <f t="shared" ref="A74:A102" si="3">RIGHT(D74,4)</f>
         <v>7564</v>
@@ -7399,7 +7399,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7149</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J76" s="27"/>
     </row>
-    <row r="77" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7233</v>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J77" s="27"/>
     </row>
-    <row r="78" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7232</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="J79" s="27"/>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7133</v>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J80" s="27"/>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="93" t="str">
         <f t="shared" si="3"/>
         <v>6946</v>
@@ -7575,7 +7575,7 @@
       <c r="I81" s="27"/>
       <c r="J81" s="27"/>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="93" t="str">
         <f t="shared" si="3"/>
         <v>6807</v>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="J82" s="27"/>
     </row>
-    <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7154</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="J86" s="27"/>
     </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7489</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="J90" s="27"/>
     </row>
-    <row r="91" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7156</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="J93" s="47"/>
     </row>
-    <row r="94" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7238</v>
@@ -8053,7 +8053,7 @@
       <c r="I97" s="13"/>
       <c r="J97" s="47"/>
     </row>
-    <row r="98" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7177</v>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="J98" s="47"/>
     </row>
-    <row r="99" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7332</v>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="J99" s="47"/>
     </row>
-    <row r="100" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7333</v>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="J100" s="47"/>
     </row>
-    <row r="101" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7608</v>
@@ -8175,7 +8175,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="93" t="str">
         <f t="shared" si="3"/>
         <v>7610</v>
@@ -8207,7 +8207,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="45"/>
       <c r="B103" s="40" t="s">
         <v>128</v>
@@ -8221,7 +8221,7 @@
       <c r="I103" s="40"/>
       <c r="J103" s="41"/>
     </row>
-    <row r="104" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="93" t="str">
         <f t="shared" ref="A104:A131" si="5">RIGHT(D104,4)</f>
         <v>3986</v>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="J104" s="27"/>
     </row>
-    <row r="105" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="93" t="str">
         <f t="shared" si="5"/>
         <v>5931</v>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="J109" s="27"/>
     </row>
-    <row r="110" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="93" t="str">
         <f t="shared" si="5"/>
         <v>4117</v>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="J112" s="27"/>
     </row>
-    <row r="113" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="93" t="str">
         <f t="shared" si="5"/>
         <v>6937</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="J114" s="27"/>
     </row>
-    <row r="115" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7147</v>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J116" s="27"/>
     </row>
-    <row r="117" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7364</v>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="J117" s="27"/>
     </row>
-    <row r="118" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7383</v>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="J118" s="27"/>
     </row>
-    <row r="119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7317</v>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J119" s="27"/>
     </row>
-    <row r="120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7318</v>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="J120" s="27"/>
     </row>
-    <row r="121" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7316</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="J121" s="27"/>
     </row>
-    <row r="122" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="93" t="str">
         <f t="shared" si="5"/>
         <v>6832</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J128" s="27"/>
     </row>
-    <row r="129" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="93" t="str">
         <f t="shared" si="5"/>
         <v>6222</v>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="J129" s="27"/>
     </row>
-    <row r="130" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="93" t="str">
         <f t="shared" si="5"/>
         <v>5679</v>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="J130" s="27"/>
     </row>
-    <row r="131" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A131" s="93" t="str">
         <f t="shared" si="5"/>
         <v>7626</v>
@@ -9097,7 +9097,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="45"/>
       <c r="B132" s="40" t="s">
         <v>160</v>
@@ -9111,7 +9111,7 @@
       <c r="I132" s="40"/>
       <c r="J132" s="41"/>
     </row>
-    <row r="133" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A133" s="93" t="str">
         <f t="shared" ref="A133:A147" si="8">RIGHT(D133,4)</f>
         <v>4584</v>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="J134" s="27"/>
     </row>
-    <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="93" t="str">
         <f t="shared" si="8"/>
         <v>6470</v>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="J135" s="27"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="93" t="str">
         <f t="shared" si="8"/>
         <v>5452</v>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J139" s="27"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="93" t="str">
         <f t="shared" si="8"/>
         <v>7377</v>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="J140" s="27"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="93" t="str">
         <f t="shared" si="8"/>
         <v>6411</v>
@@ -9385,7 +9385,7 @@
       <c r="I141" s="27"/>
       <c r="J141" s="27"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="93" t="str">
         <f t="shared" si="8"/>
         <v>6925</v>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="J142" s="27"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="93" t="str">
         <f t="shared" si="8"/>
         <v>6025</v>
@@ -9501,7 +9501,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="93" t="str">
         <f t="shared" si="8"/>
         <v>7647</v>
@@ -9533,7 +9533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="93" t="str">
         <f t="shared" si="8"/>
         <v>7651</v>
@@ -9567,7 +9567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="45"/>
       <c r="B148" s="40" t="s">
         <v>176</v>
@@ -9581,7 +9581,7 @@
       <c r="I148" s="40"/>
       <c r="J148" s="41"/>
     </row>
-    <row r="149" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="93" t="str">
         <f t="shared" ref="A149:A162" si="9">RIGHT(D149,4)</f>
         <v>7090</v>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="J153" s="27"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="93" t="str">
         <f t="shared" si="9"/>
         <v>7092</v>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="J155" s="27"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="93" t="str">
         <f t="shared" si="9"/>
         <v>6448</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="J156" s="27"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="93" t="str">
         <f t="shared" si="9"/>
         <v>6208</v>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="J157" s="27"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="93" t="str">
         <f t="shared" si="9"/>
         <v>6754</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="J159" s="27"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="93" t="str">
         <f t="shared" si="9"/>
         <v>7612</v>
@@ -24986,7 +24986,13 @@
       <c r="J1658" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J134" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J163" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
